--- a/AAII_Financials/Quarterly/BDORY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BDORY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="92">
   <si>
     <t>BDORY</t>
   </si>
@@ -656,74 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,8 +772,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +822,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +872,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -882,8 +894,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,8 +942,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,8 +992,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1023,8 +1042,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1070,8 +1092,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,8 +1111,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1133,8 +1159,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,8 +1209,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,8 +1231,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1246,8 +1279,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1293,8 +1329,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,8 +1379,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1387,8 +1429,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1434,8 +1479,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,8 +1529,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1528,8 +1579,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1575,8 +1629,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1679,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1729,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1779,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,8 +1829,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1810,8 +1879,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1857,8 +1929,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,8 +1979,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1951,60 +2029,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2106,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,164 +2126,174 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12121200</v>
+      </c>
+      <c r="E41" s="3">
         <v>11634300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10770100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11131000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11306200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12081400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13444500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13999800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13258400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13851100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10004000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11867400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>13093200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10427600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12242000</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>44916900</v>
+      </c>
+      <c r="E42" s="3">
         <v>51366000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>597200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>617300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>47060600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2393000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>55156900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>94704400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>67526000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>87078100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>84209300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3759500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3926900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3277000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>72161700</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2333900</v>
+      </c>
+      <c r="E43" s="3">
         <v>3252100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3044700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3146700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3338300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3363000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11273000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3501300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13286700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13317500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9731900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6860300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8098100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2662500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2589300</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>9900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10200</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2229,243 +2324,261 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3061100</v>
+      </c>
+      <c r="E45" s="3">
         <v>9942700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8525100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8810800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9191300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10853000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5156000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>17310100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4979700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4298200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7954100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10161900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10250800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14298900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7780500</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>89297800</v>
+      </c>
+      <c r="E46" s="3">
         <v>100097500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>49978600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>51653500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>93758500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>48960500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>103983500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>151836400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>120914300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>140965200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>133006300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>52706600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>55632100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>49570600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>113194900</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>163908700</v>
+      </c>
+      <c r="E47" s="3">
         <v>148457000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>164145700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>169646500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>116281500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>151205000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>98635100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>99229900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>107630900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>104720900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>99414200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>193714500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>174090200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>171436500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>83766500</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3709500</v>
+      </c>
+      <c r="E48" s="3">
         <v>3464500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3181100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3287700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2540200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2180300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1859300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1980200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1838000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2012700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2075800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1919700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1971800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1715000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2496900</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2367600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2248400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2185000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2258200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2195000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2018100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1833000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1958200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1877500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2089500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2225900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2138800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2278300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2115100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2086600</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2624,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2674,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4460800</v>
+      </c>
+      <c r="E52" s="3">
         <v>9175100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9130200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9436200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7768600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5663500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7871000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5346200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7978700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9201500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8846800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9065300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9227500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10235200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8513400</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2774,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>499556800</v>
+      </c>
+      <c r="E54" s="3">
         <v>499584300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>445101800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>460018100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>447343100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>422253800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>393517800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>453534500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>425637000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>459581600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>447721700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>450313500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>436184800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>417644800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>379860100</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2846,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,290 +2866,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>197862100</v>
+      </c>
+      <c r="E57" s="3">
         <v>189947500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>168996300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>174659700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>166415600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>155334100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>145353000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>160418700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>152292900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>163912000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>172221500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>160113100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>166338700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>154495400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>147010200</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>151583700</v>
+      </c>
+      <c r="E58" s="3">
         <v>150910700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>17766700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18362100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>132207500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>133285000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>129559600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>163503800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>147936900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>162209600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>147201200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>171096900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>151064100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>152290500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>523000</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>34944700</v>
+      </c>
+      <c r="E59" s="3">
         <v>15747700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14930400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15430800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15317600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13098600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12538700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14703700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14234800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13930500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14658200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14812100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14978200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13619200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10255600</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>384390400</v>
+      </c>
+      <c r="E60" s="3">
         <v>356605900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>203015900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>209819400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>313940700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>302261400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>287451300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>338626200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>314464500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>340052100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>334080900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>346022000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>332380900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>320405100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>165877400</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>56096900</v>
+      </c>
+      <c r="E61" s="3">
         <v>64235600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>170041900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>175740400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>64185500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>54989100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>37373600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>39529000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>38474400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>42787700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>41162600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>38111600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>34716200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>33726500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>163198300</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19858200</v>
+      </c>
+      <c r="E62" s="3">
         <v>35692500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>32896600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>33999100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>30737000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>28246100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>32896400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>35130200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>34570000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>34296900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>30448300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25853100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>28200000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24758000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15121800</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3214,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3264,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3314,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>462734700</v>
+      </c>
+      <c r="E66" s="3">
         <v>462216000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>410224300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>423971800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>413657000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>390128600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>362786100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>419115300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>392884100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>423888100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>412052800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>416171000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>401408700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>384163400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>348929500</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3386,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3434,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,8 +3484,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3367,8 +3534,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,55 +3584,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15271100</v>
+      </c>
+      <c r="E72" s="3">
         <v>16202100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>14942200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15442900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13989400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12842100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>13131200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13999800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12818100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13177300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12603100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11153700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10482100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14881500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12085100</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3684,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3734,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3784,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>35917100</v>
+      </c>
+      <c r="E76" s="3">
         <v>36399400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>34114300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>35257600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>32909700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>31256000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>30004000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>33486700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>31983800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>34734300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>34904200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>33276700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>33998000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>32649600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>30200400</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,60 +3884,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3795,8 +3989,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,55 +4011,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E83" s="3">
         <v>187000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>27100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>81800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>76100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>83700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>86900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>83100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>44800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>114400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>93100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>27000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>69100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>76200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>117400</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4109,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4159,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4209,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4259,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,55 +4309,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-520600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3708300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6035500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6237800</v>
       </c>
-      <c r="G89" s="3">
-        <v>1293800</v>
-      </c>
       <c r="H89" s="3">
+        <v>2215400</v>
+      </c>
+      <c r="I89" s="3">
         <v>9355000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7688400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14169600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4901600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13005400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2741600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2697100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1750500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1979500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>308800</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,55 +4381,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-174800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-210500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-181700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-187800</v>
       </c>
-      <c r="G91" s="3">
-        <v>-148300</v>
-      </c>
       <c r="H91" s="3">
+        <v>-141400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-142400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-144400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-176600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-90500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-190200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-99200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-253900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-58300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-143000</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4479,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,55 +4529,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1903900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1694600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7840000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8102800</v>
       </c>
-      <c r="G94" s="3">
-        <v>-4983800</v>
-      </c>
       <c r="H94" s="3">
+        <v>-4956300</v>
+      </c>
+      <c r="I94" s="3">
         <v>-9528400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12098700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>8636300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6699100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5708500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3851400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2486000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>3105700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2567700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>3551800</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,55 +4601,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E96" s="3">
         <v>313400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>61000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>63100</v>
       </c>
-      <c r="G96" s="3">
-        <v>444900</v>
-      </c>
       <c r="H96" s="3">
+        <v>485400</v>
+      </c>
+      <c r="I96" s="3">
         <v>625100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>483400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>684500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>680800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>708100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>604900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>647200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>660600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>705300</v>
       </c>
-      <c r="Q96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4699,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4749,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,145 +4799,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3162900</v>
+      </c>
+      <c r="E100" s="3">
         <v>6272000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1313500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1357500</v>
       </c>
-      <c r="G100" s="3">
-        <v>2989300</v>
-      </c>
       <c r="H100" s="3">
+        <v>2040200</v>
+      </c>
+      <c r="I100" s="3">
         <v>-1004500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3435700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4869600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2320600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3490400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6642300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>353300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1752800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2937400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-28500</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-506000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-855100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1322800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-210000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1041600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>197900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2208100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>161000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-867100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-350700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-308300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>9900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>500200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1376400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>147500</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>641700</v>
+      </c>
+      <c r="E102" s="3">
         <v>394400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-481100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-497200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1206800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2033000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>348200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-873600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1564700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4004400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2158800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>303300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2240900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2699900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3523900</v>
       </c>
     </row>
